--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_200_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_200_R20.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9828</v>
+        <v>11.9993</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5728</v>
+        <v>11.4549</v>
       </c>
       <c r="F2" t="n">
-        <v>0.41</v>
+        <v>0.5444</v>
       </c>
       <c r="G2" t="n">
         <v>9.3963</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5553</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8188</v>
+        <v>-0.6844</v>
       </c>
       <c r="V2" t="n">
         <v>1.7501</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9838</v>
+        <v>6.2761</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9358</v>
+        <v>5.2281</v>
       </c>
       <c r="F3" t="n">
         <v>1.048</v>
@@ -688,10 +688,10 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6054</v>
+        <v>-0.1024</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9006</v>
+        <v>0.1928</v>
       </c>
       <c r="U3" t="n">
         <v>-0.2952</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0832</v>
+        <v>4.9837</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2353</v>
+        <v>4.7072</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8479</v>
+        <v>0.2766</v>
       </c>
       <c r="G4" t="n">
         <v>4.5285</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6409</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7468</v>
+        <v>-0.275</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1059</v>
+        <v>-0.4654</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3558</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9573</v>
+        <v>2.2104</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8452</v>
+        <v>1.199</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1121</v>
+        <v>1.0113</v>
       </c>
       <c r="G5" t="n">
         <v>1.7753</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3387</v>
+        <v>-0.0857</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1094</v>
+        <v>0.0086</v>
       </c>
       <c r="V5" t="n">
         <v>2.1444</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3965</v>
+        <v>-0.2615</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1993</v>
+        <v>0.4352</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5959</v>
+        <v>-0.6967</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4449</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8615</v>
+        <v>-0.7264</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5627</v>
+        <v>-0.6636</v>
       </c>
       <c r="V6" t="n">
         <v>1.214</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3029</v>
+        <v>-1.5895</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4373</v>
+        <v>-0.7912</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8655</v>
+        <v>-0.7983</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8091</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2021</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4129</v>
+        <v>0.0591</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2922</v>
+        <v>-2.0283</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6121</v>
+        <v>0.6082</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6801</v>
+        <v>-2.6365</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2449</v>
+        <v>-0.5305</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3348</v>
+        <v>0.1921</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9101</v>
+        <v>-0.7227</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0704</v>
+        <v>0.8204</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0336</v>
+        <v>0.1211</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>0.6993</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3153</v>
+        <v>-1.3509</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3684</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9469</v>
+        <v>-1.422</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8083</v>
+        <v>-0.2812</v>
       </c>
       <c r="T8" t="n">
-        <v>0.637</v>
+        <v>-0.2122</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1713</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6002</v>
+        <v>-2.5211</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3723</v>
+        <v>-1.2572</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9726</v>
+        <v>-1.2639</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5305</v>
+        <v>-0.8708</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1921</v>
+        <v>-1.132</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7227</v>
+        <v>0.2612</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8204</v>
+        <v>0.1157</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1211</v>
+        <v>-0.3627</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6993</v>
+        <v>0.4785</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3509</v>
+        <v>-0.9865</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.7692</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.422</v>
+        <v>-0.2173</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8531</v>
+        <v>-0.8101</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>-0.1256</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.405</v>
+        <v>-0.6844</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
         <v>-2.1444</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1274</v>
+        <v>-2.7133</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.729</v>
+        <v>-1.966</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3983</v>
+        <v>-0.7473</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8708</v>
+        <v>-1.2449</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.132</v>
+        <v>-0.3348</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2612</v>
+        <v>-0.9101</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1157</v>
+        <v>0.0704</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3627</v>
+        <v>0.0336</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4785</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9865</v>
+        <v>-1.3153</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7692</v>
+        <v>-0.3684</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2173</v>
+        <v>-0.9469</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q10" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4163</v>
+        <v>0.3872</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>0.2831</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8188</v>
+        <v>0.1041</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.4483</v>
+        <v>-8.5162</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4438</v>
+        <v>-6.6797</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0045</v>
+        <v>-1.8365</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8956</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6664</v>
+        <v>-0.7343</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1889</v>
+        <v>-0.047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.6873</v>
       </c>
       <c r="V11" t="n">
         <v>1.0722</v>
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.839600000000001</v>
+        <v>7.839599999999995</v>
       </c>
       <c r="E12" t="n">
         <v>12.9385</v>
@@ -1360,10 +1360,10 @@
         <v>4.717900000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>9.703800000000001</v>
+        <v>9.703799999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>24.9475</v>
+        <v>24.94749999999999</v>
       </c>
       <c r="K12" t="n">
         <v>7.315</v>
@@ -1390,19 +1390,19 @@
         <v>15.077</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7164</v>
+        <v>-3.716699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1362000000000002</v>
+        <v>-0.1361999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.5801</v>
+        <v>-3.5802</v>
       </c>
       <c r="V12" t="n">
         <v>2.933</v>
       </c>
       <c r="W12" t="n">
-        <v>9.003000000000002</v>
+        <v>9.003</v>
       </c>
       <c r="X12" t="n">
         <v>-6.07</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5691</v>
+        <v>4.5926</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4189</v>
+        <v>7.2586</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1502</v>
+        <v>-2.666</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1624</v>
+        <v>0.1315</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8656</v>
+        <v>0.3624</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0281</v>
+        <v>-0.2309</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4814</v>
+        <v>3.9198</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4433</v>
+        <v>1.0993</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9247</v>
+        <v>2.8205</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.319</v>
+        <v>-3.7883</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4223</v>
+        <v>-0.7369</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8966</v>
+        <v>-3.0514</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5536</v>
+        <v>0.2291</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3318</v>
+        <v>0.1221</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2219</v>
+        <v>0.107</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.4665</v>
+        <v>2.1444</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3943</v>
+        <v>3.2166</v>
       </c>
       <c r="X13" t="n">
         <v>-1.0722</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6934</v>
+        <v>4.1036</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2586</v>
+        <v>4.1214</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.5652</v>
+        <v>-0.0179</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1315</v>
+        <v>2.1624</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3624</v>
+        <v>-0.8656</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2309</v>
+        <v>3.0281</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9198</v>
+        <v>3.4814</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0993</v>
+        <v>-0.4433</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8205</v>
+        <v>3.9247</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7883</v>
+        <v>-1.319</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7369</v>
+        <v>-0.4223</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.0514</v>
+        <v>-0.8966</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3299</v>
+        <v>1.0881</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1221</v>
+        <v>1.0343</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2078</v>
+        <v>0.0538</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1444</v>
+        <v>-1.4665</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2166</v>
+        <v>-0.3943</v>
       </c>
       <c r="X14" t="n">
         <v>-1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1449</v>
+        <v>0.4093</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1812</v>
+        <v>1.1956</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3262</v>
+        <v>-0.7863</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.7975</v>
+        <v>0.1217</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.82</v>
+        <v>-0.7382</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.9775</v>
+        <v>0.8598</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.0897</v>
+        <v>2.7635</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.43</v>
+        <v>0.6925</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6597</v>
+        <v>2.071</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7078</v>
+        <v>-2.6418</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.39</v>
+        <v>-1.4306</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3178</v>
+        <v>-1.2112</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8549</v>
+        <v>0.2155</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9085</v>
+        <v>0.3031</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0536</v>
+        <v>-0.0876</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2675</v>
+        <v>-0.0238</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3581</v>
+        <v>-1.4171</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6256</v>
+        <v>1.3934</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8316</v>
+        <v>-2.7975</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5774</v>
+        <v>-0.82</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2542</v>
+        <v>-1.9775</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5268</v>
+        <v>-2.0897</v>
       </c>
       <c r="K16" t="n">
-        <v>0.306</v>
+        <v>-0.43</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2208</v>
+        <v>-1.6597</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3584</v>
+        <v>-0.7078</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8834</v>
+        <v>-0.39</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4751</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6337</v>
+        <v>0.6862</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1508</v>
+        <v>0.6726</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5171</v>
+        <v>0.0136</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1069</v>
+        <v>-1.0431</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2198</v>
+        <v>-0.5855</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8871</v>
+        <v>-0.4575</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1217</v>
+        <v>-0.8316</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7382</v>
+        <v>-0.5774</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8598</v>
+        <v>-0.2542</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7635</v>
+        <v>0.5268</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6925</v>
+        <v>0.306</v>
       </c>
       <c r="L17" t="n">
-        <v>2.071</v>
+        <v>0.2208</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6418</v>
+        <v>-1.3584</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4306</v>
+        <v>-0.8834</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2112</v>
+        <v>-0.4751</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3008</v>
+        <v>0.8582</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1123</v>
+        <v>1.2072</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1885</v>
+        <v>-0.349</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5774</v>
+        <v>-1.4442</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0011</v>
+        <v>0.214</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5763</v>
+        <v>-1.6582</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2733</v>
+        <v>1.2276</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3469</v>
+        <v>-1.138</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0736</v>
+        <v>2.3656</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0736</v>
+        <v>3.9329</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.4334</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>4.3664</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3469</v>
+        <v>-2.7053</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3469</v>
+        <v>-0.7045</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-2.0008</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.232</v>
+        <v>-0.5327</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0747</v>
+        <v>-0.2396</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1573</v>
+        <v>-0.293</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7638</v>
+        <v>-1.4595</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0961</v>
+        <v>0.1169</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8599</v>
+        <v>-1.5763</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2276</v>
+        <v>-0.2733</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.138</v>
+        <v>-0.3469</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3656</v>
+        <v>0.0736</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9329</v>
+        <v>0.0736</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4334</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4.3664</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7053</v>
+        <v>-0.3469</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7045</v>
+        <v>-0.3469</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0008</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8522</v>
+        <v>-0.114</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3576</v>
+        <v>0.0433</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4946</v>
+        <v>-0.1573</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1407</v>
+        <v>-2.0563</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3681</v>
+        <v>-1.2501</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7726</v>
+        <v>-0.8062</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9714</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0127</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1937</v>
+        <v>0.1601</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8287</v>
+        <v>-3.2665</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5592</v>
+        <v>-2.5258</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.388</v>
+        <v>-0.7407</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.2437</v>
+        <v>-3.9084</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-1.3086</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6505</v>
+        <v>-2.5998</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3309</v>
+        <v>-1.1815</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6153999999999999</v>
+        <v>-0.897</v>
       </c>
       <c r="L21" t="n">
         <v>-0.2845</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.5746</v>
+        <v>-2.7269</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2087</v>
+        <v>-0.4116</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.366</v>
+        <v>-2.3153</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0798</v>
+        <v>0.3224</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9085</v>
+        <v>-0.1845</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1713</v>
+        <v>0.507</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5671</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6393</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8632</v>
+        <v>-3.4857</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5258</v>
+        <v>-0.0305</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3374</v>
+        <v>-3.4552</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9084</v>
+        <v>-4.2437</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3086</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5998</v>
+        <v>-3.6505</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1815</v>
+        <v>0.3309</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.897</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="L22" t="n">
         <v>-0.2845</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7269</v>
+        <v>-4.5746</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4116</v>
+        <v>-1.2087</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.3153</v>
+        <v>-3.366</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7257</v>
+        <v>0.4228</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1845</v>
+        <v>0.3187</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9102</v>
+        <v>0.1041</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>0.5671</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6393</v>
       </c>
       <c r="X22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6988</v>
+        <v>-4.1661</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2959</v>
+        <v>-1.9985</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4029</v>
+        <v>-2.1676</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0391</v>
@@ -2248,13 +2248,13 @@
         <v>2.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9792</v>
+        <v>0.5535</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8215</v>
+        <v>0.476</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1577</v>
+        <v>0.0775</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.839600000000001</v>
+        <v>-7.839699999999999</v>
       </c>
       <c r="E24" t="n">
         <v>5.099</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.9386</v>
+        <v>-12.9385</v>
       </c>
       <c r="G24" t="n">
         <v>-14.4218</v>
@@ -2305,7 +2305,7 @@
         <v>2.5968</v>
       </c>
       <c r="L24" t="n">
-        <v>7.928800000000001</v>
+        <v>7.928800000000003</v>
       </c>
       <c r="M24" t="n">
         <v>-24.9474</v>
@@ -2326,13 +2326,13 @@
         <v>20.8758</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7163</v>
+        <v>3.7164</v>
       </c>
       <c r="T24" t="n">
         <v>3.5803</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1361000000000001</v>
+        <v>0.1362000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-2.9331</v>
